--- a/downloads/purchasing/dixani-purchase-order-template.xlsx
+++ b/downloads/purchasing/dixani-purchase-order-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order" sheetId="1" r:id="R428e87f6d41a4973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="Reda584a0f0a2407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order" sheetId="1" r:id="R46a03aa904164a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="R9b35efa1c42946d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -448,7 +448,9 @@
       <x:c r="K4" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="L4"/>
+      <x:c r="L4" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="M4" t="str">
         <x:v>Status</x:v>
       </x:c>
@@ -1407,7 +1409,7 @@
   </x:mergeCells>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="L4">
-      <x:formula1>"QAR,USD,EUR,GBP,AED,SAR,LKR,INR"</x:formula1>
+      <x:formula1>"USD,EUR,GBP,CAD,AUD,NZD,CHF,JPY,CNY,HKD,SGD,INR,AED,SAR,QAR,LKR,ZAR,BRL,MXN"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="N4">
       <x:formula1>"Draft,Issued,Partially Received,Completed,Cancelled"</x:formula1>
